--- a/개발 현황.xlsx
+++ b/개발 현황.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이슈 목록" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이슈 목록'!$A$1:$N$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'이슈 목록'!$A$1:$N$194</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 시각 2026-07-29 10:41 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
+          <t>생성 시각 2026-07-29 12:15 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -653,7 +653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N193"/>
+  <dimension ref="A1:N194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -875,7 +875,7 @@
       </c>
       <c r="M4" s="5" t="inlineStr">
         <is>
-          <t>enhancement</t>
+          <t>enhancement, 필수</t>
         </is>
       </c>
       <c r="N4" s="5" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L28" s="5" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>bug, 생산 필수</t>
+          <t>bug, 생산 필수, 필수</t>
         </is>
       </c>
       <c r="N28" s="5" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>생산 필수</t>
+          <t>생산 필수, 필수</t>
         </is>
       </c>
       <c r="N39" s="5" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L40" s="5" t="n">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="M40" s="5" t="inlineStr">
         <is>
-          <t>생산 필수</t>
+          <t>생산 필수, 필수</t>
         </is>
       </c>
       <c r="N40" s="5" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L41" s="5" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>생산 필수</t>
+          <t>생산 필수, 필수</t>
         </is>
       </c>
       <c r="N41" s="5" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="K109" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="L109" s="5" t="n">
@@ -6743,7 +6743,7 @@
       </c>
       <c r="M109" s="5" t="inlineStr">
         <is>
-          <t>생산 필수, backfill</t>
+          <t>생산 필수, backfill, 필수</t>
         </is>
       </c>
       <c r="N109" s="5" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="M180" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 담당자 피드백</t>
         </is>
       </c>
       <c r="N180" s="5" t="inlineStr">
@@ -10495,7 +10495,7 @@
       </c>
       <c r="M181" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 담당자 피드백</t>
         </is>
       </c>
       <c r="N181" s="5" t="inlineStr">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="M182" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 담당자 피드백</t>
         </is>
       </c>
       <c r="N182" s="5" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="M183" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 담당자 피드백</t>
         </is>
       </c>
       <c r="N183" s="5" t="inlineStr">
@@ -10647,7 +10647,7 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 담당자 피드백</t>
         </is>
       </c>
       <c r="N184" s="5" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="M185" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N185" s="5" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="M186" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N186" s="5" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="M187" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N187" s="5" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="M188" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N188" s="5" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="M189" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N189" s="5" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="M190" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N190" s="5" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="M191" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N191" s="5" t="inlineStr">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="M192" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 출처: 내부 요청</t>
         </is>
       </c>
       <c r="N192" s="5" t="inlineStr">
@@ -11112,8 +11112,56 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" s="5" t="n">
+        <v>196</v>
+      </c>
+      <c r="B194" s="6" t="inlineStr">
+        <is>
+          <t>워크플로우 경합 검증 — 즉시 삭제 예정</t>
+        </is>
+      </c>
+      <c r="C194" s="5" t="inlineStr">
+        <is>
+          <t>미채택</t>
+        </is>
+      </c>
+      <c r="D194" s="5" t="inlineStr"/>
+      <c r="E194" s="5" t="inlineStr"/>
+      <c r="F194" s="5" t="inlineStr"/>
+      <c r="G194" s="5" t="inlineStr"/>
+      <c r="H194" s="5" t="inlineStr"/>
+      <c r="I194" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J194" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M194" s="5" t="inlineStr">
+        <is>
+          <t>tracking-migrated</t>
+        </is>
+      </c>
+      <c r="N194" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/uuuuj/a2z/issues/196</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N193"/>
+  <autoFilter ref="A1:N194"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/개발 현황.xlsx
+++ b/개발 현황.xlsx
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 시각 2026-07-30 13:35 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
+          <t>생성 시각 2026-07-30 14:01 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
         </is>
       </c>
     </row>
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -573,7 +573,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -640,21 +640,21 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>진행 중 · 분석 필요</t>
+          <t>진행 중 · 개발 대기</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>진행 중 · 개발 대기</t>
+          <t>진행 중 · 분석 필요</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>개발 대기</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr"/>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="M47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N47" s="5" t="n">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="M55" s="5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N55" s="5" t="n">
@@ -4726,11 +4726,11 @@
       </c>
       <c r="M68" s="5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N68" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
@@ -7760,7 +7760,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -7774,7 +7774,11 @@
       <c r="H114" s="5" t="inlineStr"/>
       <c r="I114" s="5" t="inlineStr"/>
       <c r="J114" s="5" t="inlineStr"/>
-      <c r="K114" s="5" t="inlineStr"/>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L114" s="5" t="inlineStr">
         <is>
           <t>2026-07-27</t>
@@ -7782,15 +7786,15 @@
       </c>
       <c r="M114" s="5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O114" s="5" t="inlineStr">
         <is>
-          <t>bug</t>
+          <t>bug, 종료: 재현 안 됨</t>
         </is>
       </c>
       <c r="P114" s="5" t="inlineStr">
@@ -8138,7 +8142,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr"/>
@@ -8152,7 +8156,11 @@
         </is>
       </c>
       <c r="J121" s="5" t="inlineStr"/>
-      <c r="K121" s="5" t="inlineStr"/>
+      <c r="K121" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L121" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -8160,15 +8168,15 @@
       </c>
       <c r="M121" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N121" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O121" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 재현 안 됨</t>
         </is>
       </c>
       <c r="P121" s="5" t="inlineStr">
@@ -10946,7 +10954,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr"/>
@@ -10960,7 +10968,11 @@
         </is>
       </c>
       <c r="J173" s="5" t="inlineStr"/>
-      <c r="K173" s="5" t="inlineStr"/>
+      <c r="K173" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L173" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -10972,11 +10984,11 @@
         </is>
       </c>
       <c r="N173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O173" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 수정 불필요</t>
         </is>
       </c>
       <c r="P173" s="5" t="inlineStr">
@@ -11046,7 +11058,7 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr"/>
@@ -11060,7 +11072,11 @@
         </is>
       </c>
       <c r="J175" s="5" t="inlineStr"/>
-      <c r="K175" s="5" t="inlineStr"/>
+      <c r="K175" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L175" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11072,11 +11088,11 @@
         </is>
       </c>
       <c r="N175" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O175" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 수정 불필요</t>
         </is>
       </c>
       <c r="P175" s="5" t="inlineStr">
@@ -11146,7 +11162,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr"/>
@@ -11160,7 +11176,11 @@
         </is>
       </c>
       <c r="J177" s="5" t="inlineStr"/>
-      <c r="K177" s="5" t="inlineStr"/>
+      <c r="K177" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L177" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11172,11 +11192,11 @@
         </is>
       </c>
       <c r="N177" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O177" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 수정 불필요</t>
         </is>
       </c>
       <c r="P177" s="5" t="inlineStr">
@@ -11196,7 +11216,7 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr"/>
@@ -11210,7 +11230,11 @@
         </is>
       </c>
       <c r="J178" s="5" t="inlineStr"/>
-      <c r="K178" s="5" t="inlineStr"/>
+      <c r="K178" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L178" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11222,11 +11246,11 @@
         </is>
       </c>
       <c r="N178" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O178" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 재현 안 됨</t>
         </is>
       </c>
       <c r="P178" s="5" t="inlineStr">
@@ -11246,7 +11270,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr"/>
@@ -11260,7 +11284,11 @@
         </is>
       </c>
       <c r="J179" s="5" t="inlineStr"/>
-      <c r="K179" s="5" t="inlineStr"/>
+      <c r="K179" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L179" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11272,11 +11300,11 @@
         </is>
       </c>
       <c r="N179" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated</t>
+          <t>tracking-migrated, 종료: 재현 안 됨</t>
         </is>
       </c>
       <c r="P179" s="5" t="inlineStr">
@@ -11512,7 +11540,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>분석 필요</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr"/>
@@ -11526,7 +11554,11 @@
         </is>
       </c>
       <c r="J184" s="5" t="inlineStr"/>
-      <c r="K184" s="5" t="inlineStr"/>
+      <c r="K184" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L184" s="5" t="inlineStr">
         <is>
           <t>2026-07-29</t>
@@ -11534,15 +11566,15 @@
       </c>
       <c r="M184" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N184" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O184" s="5" t="inlineStr">
         <is>
-          <t>tracking-migrated, 출처: 담당자 피드백</t>
+          <t>tracking-migrated, 출처: 담당자 피드백, 종료: 재현 안 됨</t>
         </is>
       </c>
       <c r="P184" s="5" t="inlineStr">
@@ -12240,7 +12272,7 @@
         </is>
       </c>
       <c r="N197" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O197" s="5" t="inlineStr">
         <is>

--- a/개발 현황.xlsx
+++ b/개발 현황.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="이슈 목록" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 목록'!$A$1:$P$197</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'이슈 목록'!$A$1:$P$199</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -511,7 +511,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 시각 2026-07-30 14:01 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
+          <t>생성 시각 2026-07-30 14:13 · 원천은 GitHub 이슈이며 이 파일은 읽기 전용 생성물입니다. 손으로 고치지 마십시오.</t>
         </is>
       </c>
     </row>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -552,7 +552,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -573,7 +573,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.9%</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -708,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -809,12 +809,12 @@
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>가공도</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -953,11 +953,11 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>117</v>
+        <v>197</v>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>가공도 단면 위주 출력·은선 정책</t>
+          <t>No Paint 표시방법 — 도면 표기 방식 확정</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>가공도</t>
+          <t>공통</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -982,27 +982,27 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/uuuuj/a2z/issues/117</t>
+          <t>https://github.com/uuuuj/a2z/issues/197</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>197</v>
+        <v>111</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>No Paint 표시방법 — 도면 표기 방식 확정</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>API 개발</t>
+          <t>PNOD 표시 — 값이 담긴 att(UDA) 키·노드 레벨 확인</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>내부 해결</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>API 대기</t>
+          <t>분석 필요</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -1017,17 +1017,17 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>https://github.com/uuuuj/a2z/issues/197</t>
+          <t>https://github.com/uuuuj/a2z/issues/111</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>111</v>
+        <v>198</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>PNOD 표시 — 값이 담긴 att(UDA) 키·노드 레벨 확인</t>
+          <t>개발에 필요한 att(UDA) 속성 정리 — 모델 변환 쪽에 일괄 요청</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -1051,41 +1051,6 @@
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>https://github.com/uuuuj/a2z/issues/111</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>198</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>개발에 필요한 att(UDA) 속성 정리 — 모델 변환 쪽에 일괄 요청</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>내부 해결</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>분석 필요</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>공통</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>https://github.com/uuuuj/a2z/issues/198</t>
         </is>
@@ -1102,7 +1067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P197"/>
+  <dimension ref="A1:P199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -2561,7 +2526,7 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>공통</t>
+          <t>가공도</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -2586,7 +2551,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Excel No.14</t>
+          <t>Excel No.14, 64</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
@@ -2602,7 +2567,7 @@
       </c>
       <c r="M28" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N28" s="5" t="n">
@@ -4730,7 +4695,7 @@
         </is>
       </c>
       <c r="N68" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
@@ -7814,7 +7779,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>API 대기</t>
+          <t>미채택</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -7827,16 +7792,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="F115" s="5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="inlineStr">
-        <is>
-          <t>API 개발</t>
-        </is>
-      </c>
+      <c r="F115" s="5" t="inlineStr"/>
+      <c r="G115" s="5" t="inlineStr"/>
       <c r="H115" s="5" t="inlineStr">
         <is>
           <t>뷰</t>
@@ -7852,7 +7809,11 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="K115" s="5" t="inlineStr"/>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
       <c r="L115" s="5" t="inlineStr">
         <is>
           <t>2026-07-27</t>
@@ -7860,15 +7821,15 @@
       </c>
       <c r="M115" s="5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="N115" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O115" s="5" t="inlineStr">
         <is>
-          <t>생산 필수, backfill</t>
+          <t>duplicate, 생산 필수, backfill</t>
         </is>
       </c>
       <c r="P115" s="5" t="inlineStr">
@@ -12285,8 +12246,116 @@
         </is>
       </c>
     </row>
+    <row r="198">
+      <c r="A198" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>ClickOnce 게시에 네이티브 DLL 5종 누락 — 설치는 되나 실행 즉시 종료</t>
+        </is>
+      </c>
+      <c r="C198" s="5" t="inlineStr">
+        <is>
+          <t>개발 대기</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr"/>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F198" s="5" t="inlineStr"/>
+      <c r="G198" s="5" t="inlineStr">
+        <is>
+          <t>내부 해결</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="inlineStr"/>
+      <c r="I198" s="5" t="inlineStr"/>
+      <c r="J198" s="5" t="inlineStr"/>
+      <c r="K198" s="5" t="inlineStr"/>
+      <c r="L198" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="M198" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N198" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O198" s="5" t="inlineStr">
+        <is>
+          <t>생산 필수</t>
+        </is>
+      </c>
+      <c r="P198" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/uuuuj/a2z/issues/200</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="5" t="n">
+        <v>201</v>
+      </c>
+      <c r="B199" s="6" t="inlineStr">
+        <is>
+          <t>ClickOnce 설치 시 도면·로그 출력 위치 — 담당자가 결과물을 찾을 수 없음</t>
+        </is>
+      </c>
+      <c r="C199" s="5" t="inlineStr">
+        <is>
+          <t>분석 필요</t>
+        </is>
+      </c>
+      <c r="D199" s="5" t="inlineStr"/>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F199" s="5" t="inlineStr"/>
+      <c r="G199" s="5" t="inlineStr">
+        <is>
+          <t>내부 해결</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="inlineStr"/>
+      <c r="I199" s="5" t="inlineStr"/>
+      <c r="J199" s="5" t="inlineStr"/>
+      <c r="K199" s="5" t="inlineStr"/>
+      <c r="L199" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="M199" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N199" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" s="5" t="inlineStr">
+        <is>
+          <t>생산 필수</t>
+        </is>
+      </c>
+      <c r="P199" s="5" t="inlineStr">
+        <is>
+          <t>https://github.com/uuuuj/a2z/issues/201</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P197"/>
+  <autoFilter ref="A1:P199"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>